--- a/FLORES DE ESTRADA/Diciembre/EDESUR Diciembre.xlsx
+++ b/FLORES DE ESTRADA/Diciembre/EDESUR Diciembre.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\Desktop\RC CONSORCIO 2025\FLORES DE ESTRADA\Noviembre\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\Desktop\RC CONSORCIO 2025\FLORES DE ESTRADA\Diciembre\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD886163-5964-4188-AC50-6FDF748E1B19}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{469B7B01-186B-47AB-923A-1C21A39499B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -233,10 +233,10 @@
     <t>7-B</t>
   </si>
   <si>
-    <t>EDESUR - VENCIMIENTO 15/12</t>
+    <t>NN</t>
   </si>
   <si>
-    <t>NN</t>
+    <t>EDESUR - VENCIMIENTO 15/01</t>
   </si>
 </sst>
 </file>
@@ -337,7 +337,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="10">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -384,12 +384,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFFF0000"/>
         <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFF0000"/>
-        <bgColor theme="0"/>
       </patternFill>
     </fill>
   </fills>
@@ -551,7 +545,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="68">
+  <cellXfs count="67">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -632,6 +626,7 @@
     <xf numFmtId="2" fontId="4" fillId="6" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="8" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="4" fillId="8" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -647,9 +642,7 @@
     <xf numFmtId="0" fontId="11" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="4" fillId="9" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="4" fillId="8" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -955,13 +948,13 @@
     <col min="3" max="3" width="14.85546875" customWidth="1"/>
     <col min="4" max="4" width="27" customWidth="1"/>
     <col min="5" max="5" width="6.42578125" customWidth="1"/>
-    <col min="6" max="6" width="10.42578125" hidden="1" customWidth="1"/>
-    <col min="7" max="7" width="8.85546875" hidden="1" customWidth="1"/>
-    <col min="8" max="8" width="7.7109375" hidden="1" customWidth="1"/>
-    <col min="9" max="9" width="10.42578125" hidden="1" customWidth="1"/>
-    <col min="10" max="10" width="13.85546875" hidden="1" customWidth="1"/>
-    <col min="11" max="11" width="15.42578125" hidden="1" customWidth="1"/>
-    <col min="12" max="12" width="11.140625" hidden="1" customWidth="1"/>
+    <col min="6" max="6" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="8.85546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="7.7109375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="13.85546875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="15.42578125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="11.140625" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="13.7109375" customWidth="1"/>
     <col min="14" max="14" width="13.5703125" hidden="1" customWidth="1"/>
     <col min="15" max="15" width="13.7109375" hidden="1" customWidth="1"/>
@@ -974,21 +967,21 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:25" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="58" t="s">
-        <v>67</v>
-      </c>
-      <c r="B1" s="59"/>
-      <c r="C1" s="59"/>
-      <c r="D1" s="59"/>
-      <c r="E1" s="59"/>
-      <c r="F1" s="59"/>
-      <c r="G1" s="59"/>
-      <c r="H1" s="59"/>
-      <c r="I1" s="59"/>
-      <c r="J1" s="59"/>
-      <c r="K1" s="59"/>
-      <c r="L1" s="59"/>
-      <c r="M1" s="60"/>
+      <c r="A1" s="59" t="s">
+        <v>68</v>
+      </c>
+      <c r="B1" s="60"/>
+      <c r="C1" s="60"/>
+      <c r="D1" s="60"/>
+      <c r="E1" s="60"/>
+      <c r="F1" s="60"/>
+      <c r="G1" s="60"/>
+      <c r="H1" s="60"/>
+      <c r="I1" s="60"/>
+      <c r="J1" s="60"/>
+      <c r="K1" s="60"/>
+      <c r="L1" s="60"/>
+      <c r="M1" s="61"/>
       <c r="N1" s="1"/>
       <c r="O1" s="2"/>
       <c r="P1" s="3"/>
@@ -1131,7 +1124,7 @@
         <v>9</v>
       </c>
       <c r="C8" s="50">
-        <v>1023447.02</v>
+        <v>1030338.54</v>
       </c>
       <c r="E8" s="10"/>
       <c r="F8" s="10"/>
@@ -1182,7 +1175,7 @@
       </c>
       <c r="L9" s="15">
         <f>C8-J34</f>
-        <v>733416.42740000016</v>
+        <v>622963.84679999994</v>
       </c>
       <c r="M9" s="14" t="s">
         <v>19</v>
@@ -1212,10 +1205,10 @@
         <v>4.9000000000000004</v>
       </c>
       <c r="F10" s="18">
-        <v>19937.5</v>
+        <v>20263.599999999999</v>
       </c>
       <c r="G10" s="51">
-        <v>20263.599999999999</v>
+        <v>20622.599999999999</v>
       </c>
       <c r="H10" s="19">
         <v>0</v>
@@ -1226,31 +1219,31 @@
       </c>
       <c r="J10" s="20">
         <f>(G10-F10)*93.78</f>
-        <v>30581.657999999865</v>
+        <v>33667.019999999997</v>
       </c>
       <c r="K10" s="21">
         <f>G10-F10</f>
-        <v>326.09999999999854</v>
+        <v>359</v>
       </c>
       <c r="L10" s="19">
         <f>L9*E10/100</f>
-        <v>35937.404942600013</v>
+        <v>30525.2284932</v>
       </c>
       <c r="M10" s="19">
         <f>J10+L10+3</f>
-        <v>66522.062942599878</v>
+        <v>64195.248493199993</v>
       </c>
       <c r="N10" s="22">
         <f>J10/C7*100</f>
-        <v>39.182137091607771</v>
+        <v>43.135195387572068</v>
       </c>
       <c r="O10" s="23">
         <f>J10/L9*100</f>
-        <v>4.1697536157478021</v>
+        <v>5.4043296690391509</v>
       </c>
       <c r="P10" s="20">
         <f>C7*O10/100</f>
-        <v>3254.4926970911597</v>
+        <v>4218.0793066850574</v>
       </c>
       <c r="Q10" s="24">
         <v>0.31</v>
@@ -1277,11 +1270,11 @@
         <v>3.89</v>
       </c>
       <c r="F11" s="52">
-        <v>17283.900000000001</v>
+        <v>17353.900000000001</v>
       </c>
       <c r="G11" s="57">
         <f>F11+70</f>
-        <v>17353.900000000001</v>
+        <v>17423.900000000001</v>
       </c>
       <c r="H11" s="53">
         <v>0</v>
@@ -1294,17 +1287,17 @@
         <f>(G11-F11)*93.78</f>
         <v>6564.6</v>
       </c>
-      <c r="K11" s="67">
+      <c r="K11" s="58">
         <f t="shared" ref="K11:K25" si="2">G11-F11</f>
         <v>70</v>
       </c>
       <c r="L11" s="53">
         <f>L9*E11/100</f>
-        <v>28529.899025860006</v>
+        <v>24233.293640520002</v>
       </c>
       <c r="M11" s="53">
         <f t="shared" ref="M11:M24" si="3">J11+L11+1</f>
-        <v>35095.499025860008</v>
+        <v>30798.89364052</v>
       </c>
       <c r="N11" s="22" t="e">
         <f t="shared" ref="N11:N33" si="4">J11/C9*100</f>
@@ -1312,11 +1305,11 @@
       </c>
       <c r="O11" s="23">
         <f>L11/L9*100</f>
-        <v>3.8899999999999997</v>
+        <v>3.8900000000000006</v>
       </c>
       <c r="P11" s="20">
         <f>C7*O11/100</f>
-        <v>3036.145</v>
+        <v>3036.1450000000004</v>
       </c>
       <c r="Q11" s="24">
         <v>0.19</v>
@@ -1344,11 +1337,11 @@
         <v>4</v>
       </c>
       <c r="F12" s="39">
-        <v>11756.3</v>
+        <v>11841.3</v>
       </c>
       <c r="G12" s="51">
         <f>F12+85</f>
-        <v>11841.3</v>
+        <v>11926.3</v>
       </c>
       <c r="H12" s="40">
         <v>0</v>
@@ -1367,11 +1360,11 @@
       </c>
       <c r="L12" s="40">
         <f>L9*E12/100</f>
-        <v>29336.657096000006</v>
+        <v>24918.553871999997</v>
       </c>
       <c r="M12" s="40">
         <f t="shared" si="3"/>
-        <v>37308.957096000006</v>
+        <v>32890.853872</v>
       </c>
       <c r="N12" s="22" t="e">
         <f t="shared" si="4"/>
@@ -1379,11 +1372,11 @@
       </c>
       <c r="O12" s="23">
         <f>J12/L9*100</f>
-        <v>1.0868723009462276</v>
+        <v>1.2795766625858713</v>
       </c>
       <c r="P12" s="20">
         <f>C7*O12/100</f>
-        <v>848.30383088853068</v>
+        <v>998.70958514827259</v>
       </c>
     </row>
     <row r="13" spans="1:25" x14ac:dyDescent="0.25">
@@ -1403,10 +1396,10 @@
         <v>4.9000000000000004</v>
       </c>
       <c r="F13" s="39">
-        <v>29923.5</v>
+        <v>30278.400000000001</v>
       </c>
       <c r="G13" s="51">
-        <v>30278.400000000001</v>
+        <v>30687.599999999999</v>
       </c>
       <c r="H13" s="26">
         <v>0</v>
@@ -1417,19 +1410,19 @@
       </c>
       <c r="J13" s="41">
         <f t="shared" si="5"/>
-        <v>33282.522000000135</v>
+        <v>38374.775999999729</v>
       </c>
       <c r="K13" s="42">
         <f t="shared" si="2"/>
-        <v>354.90000000000146</v>
+        <v>409.19999999999709</v>
       </c>
       <c r="L13" s="40">
         <f>L9*E13/100</f>
-        <v>35937.404942600013</v>
+        <v>30525.2284932</v>
       </c>
       <c r="M13" s="40">
         <f t="shared" si="3"/>
-        <v>69220.926942600141</v>
+        <v>68901.004493199725</v>
       </c>
       <c r="N13" s="22" t="e">
         <f t="shared" si="4"/>
@@ -1437,11 +1430,11 @@
       </c>
       <c r="O13" s="23">
         <f>J13/L9*100</f>
-        <v>4.5380115247743262</v>
+        <v>6.1600325921192338</v>
       </c>
       <c r="P13" s="20">
         <f>C7*O13/100</f>
-        <v>3541.9179950863618</v>
+        <v>4807.9054381490623</v>
       </c>
     </row>
     <row r="14" spans="1:25" x14ac:dyDescent="0.25">
@@ -1461,10 +1454,10 @@
         <v>3.89</v>
       </c>
       <c r="F14" s="39">
-        <v>7341.7</v>
+        <v>7623.9</v>
       </c>
       <c r="G14" s="51">
-        <v>7623.9</v>
+        <v>8042.5</v>
       </c>
       <c r="H14" s="26">
         <v>0</v>
@@ -1475,19 +1468,19 @@
       </c>
       <c r="J14" s="41">
         <f t="shared" si="5"/>
-        <v>26464.715999999982</v>
+        <v>39256.308000000034</v>
       </c>
       <c r="K14" s="42">
         <f t="shared" si="2"/>
-        <v>282.19999999999982</v>
+        <v>418.60000000000036</v>
       </c>
       <c r="L14" s="40">
         <f>L9*E14/100</f>
-        <v>28529.899025860006</v>
+        <v>24233.293640520002</v>
       </c>
       <c r="M14" s="40">
         <f t="shared" si="3"/>
-        <v>54995.615025859988</v>
+        <v>63490.601640520035</v>
       </c>
       <c r="N14" s="22" t="e">
         <f t="shared" si="4"/>
@@ -1495,11 +1488,11 @@
       </c>
       <c r="O14" s="23">
         <f>J14/L9*100</f>
-        <v>3.6084160391414732</v>
+        <v>6.3015387171581905</v>
       </c>
       <c r="P14" s="20">
         <f>C7*O14/100</f>
-        <v>2816.3687185499202</v>
+        <v>4918.3509687419682</v>
       </c>
       <c r="R14">
         <v>2540.8200000000002</v>
@@ -1522,11 +1515,11 @@
         <v>4</v>
       </c>
       <c r="F15" s="36">
-        <v>14436.7</v>
+        <v>14706.7</v>
       </c>
       <c r="G15" s="56">
         <f>F15+270</f>
-        <v>14706.7</v>
+        <v>14976.7</v>
       </c>
       <c r="H15" s="37">
         <v>0</v>
@@ -1545,11 +1538,11 @@
       </c>
       <c r="L15" s="37">
         <f>L9*E15/100</f>
-        <v>29336.657096000006</v>
+        <v>24918.553871999997</v>
       </c>
       <c r="M15" s="37">
         <f t="shared" si="3"/>
-        <v>54658.257096000001</v>
+        <v>50240.153871999995</v>
       </c>
       <c r="N15" s="46" t="e">
         <f t="shared" si="4"/>
@@ -1557,11 +1550,11 @@
       </c>
       <c r="O15" s="47">
         <f>J15/L9*100</f>
-        <v>3.4524178971233113</v>
+        <v>4.0645376340962969</v>
       </c>
       <c r="P15" s="41">
         <f>C7*O15/100</f>
-        <v>2694.6121687047444</v>
+        <v>3172.3716234121598</v>
       </c>
       <c r="Y15" s="49"/>
     </row>
@@ -1582,10 +1575,10 @@
         <v>4.9000000000000004</v>
       </c>
       <c r="F16" s="18">
-        <v>19858.7</v>
+        <v>20071.5</v>
       </c>
       <c r="G16" s="51">
-        <v>20071.5</v>
+        <v>20484.8</v>
       </c>
       <c r="H16" s="19">
         <v>0</v>
@@ -1596,19 +1589,19 @@
       </c>
       <c r="J16" s="20">
         <f t="shared" si="5"/>
-        <v>19956.383999999933</v>
+        <v>38759.273999999932</v>
       </c>
       <c r="K16" s="21">
         <f t="shared" si="2"/>
-        <v>212.79999999999927</v>
+        <v>413.29999999999927</v>
       </c>
       <c r="L16" s="19">
         <f>L9*E16/100</f>
-        <v>35937.404942600013</v>
+        <v>30525.2284932</v>
       </c>
       <c r="M16" s="19">
         <f t="shared" si="3"/>
-        <v>55894.788942599946</v>
+        <v>69285.502493199936</v>
       </c>
       <c r="N16" s="22" t="e">
         <f t="shared" si="4"/>
@@ -1616,11 +1609,11 @@
       </c>
       <c r="O16" s="23">
         <f>J16/L9*100</f>
-        <v>2.7210167722512524</v>
+        <v>6.2217533487851728</v>
       </c>
       <c r="P16" s="20">
         <f>C7*O16/100</f>
-        <v>2123.7535907421025</v>
+        <v>4856.0784887268273</v>
       </c>
     </row>
     <row r="17" spans="1:19" x14ac:dyDescent="0.25">
@@ -1640,10 +1633,10 @@
         <v>3.89</v>
       </c>
       <c r="F17" s="18">
-        <v>6646.43</v>
+        <v>6715.4</v>
       </c>
       <c r="G17" s="51">
-        <v>6715.4</v>
+        <v>6829.25</v>
       </c>
       <c r="H17" s="26">
         <v>0</v>
@@ -1654,19 +1647,19 @@
       </c>
       <c r="J17" s="20">
         <f t="shared" si="5"/>
-        <v>6468.0065999999388</v>
+        <v>10676.853000000034</v>
       </c>
       <c r="K17" s="21">
         <f t="shared" si="2"/>
-        <v>68.969999999999345</v>
+        <v>113.85000000000036</v>
       </c>
       <c r="L17" s="19">
         <f>L9*E17/100</f>
-        <v>28529.899025860006</v>
+        <v>24233.293640520002</v>
       </c>
       <c r="M17" s="19">
         <f t="shared" si="3"/>
-        <v>34998.905625859945</v>
+        <v>34911.146640520034</v>
       </c>
       <c r="N17" s="22" t="e">
         <f t="shared" si="4"/>
@@ -1674,11 +1667,11 @@
       </c>
       <c r="O17" s="23">
         <f>J17/L9*100</f>
-        <v>0.88190097172071291</v>
+        <v>1.7138800357106108</v>
       </c>
       <c r="P17" s="20">
         <f>C7*O17/100</f>
-        <v>688.3237084280164</v>
+        <v>1337.6833678721316</v>
       </c>
     </row>
     <row r="18" spans="1:19" x14ac:dyDescent="0.25">
@@ -1698,10 +1691,11 @@
         <v>4</v>
       </c>
       <c r="F18" s="39">
-        <v>22070.9</v>
+        <v>22279.9</v>
       </c>
       <c r="G18" s="51">
-        <v>22279.9</v>
+        <f>F18+209</f>
+        <v>22488.9</v>
       </c>
       <c r="H18" s="45">
         <v>0</v>
@@ -1720,11 +1714,11 @@
       </c>
       <c r="L18" s="40">
         <f>L9*E18/100</f>
-        <v>29336.657096000006</v>
+        <v>24918.553871999997</v>
       </c>
       <c r="M18" s="40">
         <f t="shared" si="3"/>
-        <v>48937.677096000007</v>
+        <v>44519.573871999994</v>
       </c>
       <c r="N18" s="22" t="e">
         <f t="shared" si="4"/>
@@ -1732,11 +1726,11 @@
       </c>
       <c r="O18" s="23">
         <f>J18/L9*100</f>
-        <v>2.6724271870324889</v>
+        <v>3.1462532056523189</v>
       </c>
       <c r="P18" s="20">
         <f>C7*O18/100</f>
-        <v>2085.8294194788577</v>
+        <v>2455.6506270116352</v>
       </c>
     </row>
     <row r="19" spans="1:19" x14ac:dyDescent="0.25">
@@ -1756,10 +1750,10 @@
         <v>12.66</v>
       </c>
       <c r="F19" s="39">
-        <v>24065</v>
+        <v>24404.2</v>
       </c>
       <c r="G19" s="51">
-        <v>24404.2</v>
+        <v>25199.5</v>
       </c>
       <c r="H19" s="40">
         <v>0</v>
@@ -1770,19 +1764,19 @@
       </c>
       <c r="J19" s="41">
         <f t="shared" si="5"/>
-        <v>31810.176000000069</v>
+        <v>74583.233999999939</v>
       </c>
       <c r="K19" s="42">
         <f t="shared" si="2"/>
-        <v>339.20000000000073</v>
+        <v>795.29999999999927</v>
       </c>
       <c r="L19" s="40">
         <f>L9*E19/100</f>
-        <v>92850.519708840031</v>
+        <v>78867.223004879997</v>
       </c>
       <c r="M19" s="40">
         <f>J19+L19+1</f>
-        <v>124661.6957088401</v>
+        <v>153451.45700487995</v>
       </c>
       <c r="N19" s="22" t="e">
         <f t="shared" si="4"/>
@@ -1790,11 +1784,11 @@
       </c>
       <c r="O19" s="23">
         <f>J19/L9*100</f>
-        <v>4.3372598174230728</v>
+        <v>11.972321408876972</v>
       </c>
       <c r="P19" s="20">
         <f>C7*O19/100</f>
-        <v>3385.2312874987083</v>
+        <v>9344.3968596284758</v>
       </c>
     </row>
     <row r="20" spans="1:19" x14ac:dyDescent="0.25">
@@ -1814,11 +1808,11 @@
         <v>7.75</v>
       </c>
       <c r="F20" s="39">
-        <v>18745.099999999999</v>
+        <v>18945.099999999999</v>
       </c>
       <c r="G20" s="51">
         <f>F20+200</f>
-        <v>18945.099999999999</v>
+        <v>19145.099999999999</v>
       </c>
       <c r="H20" s="26">
         <v>0</v>
@@ -1837,11 +1831,11 @@
       </c>
       <c r="L20" s="40">
         <f>L9*E20/100</f>
-        <v>56839.77312350001</v>
+        <v>48279.698126999996</v>
       </c>
       <c r="M20" s="40">
         <f t="shared" si="3"/>
-        <v>75596.77312350001</v>
+        <v>67036.698126999996</v>
       </c>
       <c r="N20" s="22" t="e">
         <f t="shared" si="4"/>
@@ -1849,57 +1843,57 @@
       </c>
       <c r="O20" s="23">
         <f>J20/L9*100</f>
-        <v>2.5573465904617119</v>
+        <v>3.0107686178491093</v>
       </c>
       <c r="P20" s="20">
         <f>C7*O20/100</f>
-        <v>1996.0090138553662</v>
+        <v>2349.9049062312297</v>
       </c>
     </row>
     <row r="21" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="36">
         <v>12</v>
       </c>
-      <c r="B21" s="52">
+      <c r="B21" s="39">
         <v>12</v>
       </c>
-      <c r="C21" s="52" t="s">
+      <c r="C21" s="39" t="s">
         <v>43</v>
       </c>
-      <c r="D21" s="65" t="s">
+      <c r="D21" s="66" t="s">
         <v>64</v>
       </c>
-      <c r="E21" s="52">
+      <c r="E21" s="39">
         <v>7.51</v>
       </c>
-      <c r="F21" s="52">
-        <v>15269.3</v>
-      </c>
-      <c r="G21" s="57">
+      <c r="F21" s="39">
         <v>15306.9</v>
       </c>
-      <c r="H21" s="66">
-        <v>0</v>
-      </c>
-      <c r="I21" s="54">
+      <c r="G21" s="51">
+        <v>15338.2</v>
+      </c>
+      <c r="H21" s="26">
+        <v>0</v>
+      </c>
+      <c r="I21" s="41">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J21" s="54">
+      <c r="J21" s="41">
         <f t="shared" si="5"/>
-        <v>3526.1280000000343</v>
-      </c>
-      <c r="K21" s="67">
+        <v>2935.3140000001022</v>
+      </c>
+      <c r="K21" s="42">
         <f t="shared" si="2"/>
-        <v>37.600000000000364</v>
-      </c>
-      <c r="L21" s="53">
+        <v>31.300000000001091</v>
+      </c>
+      <c r="L21" s="40">
         <f>L9*E21/100</f>
-        <v>55079.573697740008</v>
-      </c>
-      <c r="M21" s="53">
+        <v>46784.584894679989</v>
+      </c>
+      <c r="M21" s="40">
         <f t="shared" si="3"/>
-        <v>58606.701697740042</v>
+        <v>49720.898894680089</v>
       </c>
       <c r="N21" s="22" t="e">
         <f t="shared" si="4"/>
@@ -1907,15 +1901,15 @@
       </c>
       <c r="O21" s="23">
         <f>J21/L9*100</f>
-        <v>0.48078115900680651</v>
+        <v>0.47118528869340198</v>
       </c>
       <c r="P21" s="20">
         <f>C7*O21/100</f>
-        <v>375.24969460481248</v>
+        <v>367.76011782520021</v>
       </c>
       <c r="S21">
         <f>G21-F21</f>
-        <v>37.600000000000364</v>
+        <v>31.300000000001091</v>
       </c>
     </row>
     <row r="22" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -1935,11 +1929,11 @@
         <v>4.45</v>
       </c>
       <c r="F22" s="39">
-        <v>11800.2</v>
+        <v>12050.2</v>
       </c>
       <c r="G22" s="51">
-        <f>F22+250</f>
-        <v>12050.2</v>
+        <f>F22+300</f>
+        <v>12350.2</v>
       </c>
       <c r="H22" s="26">
         <v>0</v>
@@ -1950,19 +1944,19 @@
       </c>
       <c r="J22" s="41">
         <f t="shared" si="5"/>
-        <v>23445</v>
+        <v>28134</v>
       </c>
       <c r="K22" s="42">
         <f t="shared" si="2"/>
-        <v>250</v>
+        <v>300</v>
       </c>
       <c r="L22" s="40">
         <f>L9*E22/100</f>
-        <v>32637.031019300008</v>
+        <v>27721.8911826</v>
       </c>
       <c r="M22" s="40">
         <f t="shared" si="3"/>
-        <v>56083.031019300004</v>
+        <v>55856.891182599997</v>
       </c>
       <c r="N22" s="22" t="e">
         <f t="shared" si="4"/>
@@ -1970,15 +1964,15 @@
       </c>
       <c r="O22" s="23">
         <f>J22/L9*100</f>
-        <v>3.1966832380771395</v>
+        <v>4.516152926773664</v>
       </c>
       <c r="P22" s="20">
         <f>C7*O22/100</f>
-        <v>2495.011267319207</v>
+        <v>3524.8573593468445</v>
       </c>
       <c r="S22">
         <f>G22-F22</f>
-        <v>250</v>
+        <v>300</v>
       </c>
     </row>
     <row r="23" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -1998,10 +1992,10 @@
         <v>6.17</v>
       </c>
       <c r="F23" s="39">
-        <v>20525.400000000001</v>
+        <v>20587.3</v>
       </c>
       <c r="G23" s="51">
-        <v>20587.3</v>
+        <v>20942.79</v>
       </c>
       <c r="H23" s="40">
         <v>0</v>
@@ -2012,19 +2006,19 @@
       </c>
       <c r="J23" s="41">
         <f t="shared" si="5"/>
-        <v>5804.9819999997953</v>
+        <v>33337.852200000154</v>
       </c>
       <c r="K23" s="42">
         <f t="shared" si="2"/>
-        <v>61.899999999997817</v>
+        <v>355.4900000000016</v>
       </c>
       <c r="L23" s="40">
         <f>L9*E23/100</f>
-        <v>45251.793570580005</v>
+        <v>38436.869347559994</v>
       </c>
       <c r="M23" s="40">
         <f>J23+L23+1</f>
-        <v>51057.775570579797</v>
+        <v>71775.721547560155</v>
       </c>
       <c r="N23" s="22" t="e">
         <f t="shared" si="4"/>
@@ -2032,11 +2026,11 @@
       </c>
       <c r="O23" s="23">
         <f>J23/L9*100</f>
-        <v>0.79149876974787192</v>
+        <v>5.3514906797959236</v>
       </c>
       <c r="P23" s="20">
         <f>C7*O23/100</f>
-        <v>617.76478978821399</v>
+        <v>4176.8384755807183</v>
       </c>
     </row>
     <row r="24" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -2056,10 +2050,11 @@
         <v>4.45</v>
       </c>
       <c r="F24" s="39">
-        <v>31291.8</v>
+        <v>31465.9</v>
       </c>
       <c r="G24" s="51">
-        <v>31465.9</v>
+        <f>F24+180</f>
+        <v>31645.9</v>
       </c>
       <c r="H24" s="40">
         <v>0</v>
@@ -2070,19 +2065,19 @@
       </c>
       <c r="J24" s="41">
         <f t="shared" si="5"/>
-        <v>16327.098000000206</v>
+        <v>16880.400000000001</v>
       </c>
       <c r="K24" s="42">
         <f t="shared" si="2"/>
-        <v>174.10000000000218</v>
+        <v>180</v>
       </c>
       <c r="L24" s="40">
         <f>L9*E24/100</f>
-        <v>32637.031019300008</v>
+        <v>27721.8911826</v>
       </c>
       <c r="M24" s="40">
         <f t="shared" si="3"/>
-        <v>48965.129019300213</v>
+        <v>44603.291182600005</v>
       </c>
       <c r="N24" s="22" t="e">
         <f t="shared" si="4"/>
@@ -2090,11 +2085,11 @@
       </c>
       <c r="O24" s="23">
         <f>J24/L9*100</f>
-        <v>2.2261702069969482</v>
+        <v>2.7096917560641987</v>
       </c>
       <c r="P24" s="20">
         <f>C7*O24/100</f>
-        <v>1737.525846561118</v>
+        <v>2114.914415608107</v>
       </c>
     </row>
     <row r="25" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -2114,10 +2109,10 @@
         <v>9.19</v>
       </c>
       <c r="F25" s="39">
-        <v>12050.9</v>
+        <v>12201.8</v>
       </c>
       <c r="G25" s="51">
-        <v>12201.8</v>
+        <v>12335.7</v>
       </c>
       <c r="H25" s="40">
         <v>0</v>
@@ -2128,19 +2123,19 @@
       </c>
       <c r="J25" s="41">
         <f t="shared" si="5"/>
-        <v>14151.401999999965</v>
+        <v>12557.142000000136</v>
       </c>
       <c r="K25" s="42">
         <f t="shared" si="2"/>
-        <v>150.89999999999964</v>
+        <v>133.90000000000146</v>
       </c>
       <c r="L25" s="40">
         <f>L9*E25/100</f>
-        <v>67400.969678060006</v>
+        <v>57250.377520919988</v>
       </c>
       <c r="M25" s="40">
         <f>J25+L25+1</f>
-        <v>81553.371678059979</v>
+        <v>69808.519520920119</v>
       </c>
       <c r="N25" s="22" t="e">
         <f t="shared" si="4"/>
@@ -2148,11 +2143,11 @@
       </c>
       <c r="O25" s="23">
         <f>J25/L9*100</f>
-        <v>1.9295180025033567</v>
+        <v>2.0157095896500006</v>
       </c>
       <c r="P25" s="20">
         <f>C7*O25/100</f>
-        <v>1505.9888009538699</v>
+        <v>1573.2613347218255</v>
       </c>
     </row>
     <row r="26" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -2191,11 +2186,11 @@
       <c r="K26" s="40"/>
       <c r="L26" s="40">
         <f>L9*E26/100</f>
-        <v>8654.313843320002</v>
+        <v>7350.9733922399992</v>
       </c>
       <c r="M26" s="40">
         <f t="shared" ref="M26:M33" si="6">J26+L26</f>
-        <v>8654.313843320002</v>
+        <v>7350.9733922399992</v>
       </c>
       <c r="N26" s="22" t="e">
         <f t="shared" si="4"/>
@@ -2246,11 +2241,11 @@
       <c r="K27" s="53"/>
       <c r="L27" s="53">
         <f>L26</f>
-        <v>8654.313843320002</v>
+        <v>7350.9733922399992</v>
       </c>
       <c r="M27" s="53">
         <f t="shared" si="6"/>
-        <v>8654.313843320002</v>
+        <v>7350.9733922399992</v>
       </c>
       <c r="N27" s="22" t="e">
         <f t="shared" si="4"/>
@@ -2301,11 +2296,11 @@
       <c r="K28" s="53"/>
       <c r="L28" s="53">
         <f>L27</f>
-        <v>8654.313843320002</v>
+        <v>7350.9733922399992</v>
       </c>
       <c r="M28" s="53">
         <f t="shared" si="6"/>
-        <v>8654.313843320002</v>
+        <v>7350.9733922399992</v>
       </c>
       <c r="N28" s="22" t="e">
         <f t="shared" si="4"/>
@@ -2356,11 +2351,11 @@
       <c r="K29" s="40"/>
       <c r="L29" s="40">
         <f>L28</f>
-        <v>8654.313843320002</v>
+        <v>7350.9733922399992</v>
       </c>
       <c r="M29" s="40">
         <f t="shared" si="6"/>
-        <v>8654.313843320002</v>
+        <v>7350.9733922399992</v>
       </c>
       <c r="N29" s="22" t="e">
         <f t="shared" si="4"/>
@@ -2411,11 +2406,11 @@
       <c r="K30" s="19"/>
       <c r="L30" s="19">
         <f t="shared" ref="L30:L33" si="7">L29</f>
-        <v>8654.313843320002</v>
+        <v>7350.9733922399992</v>
       </c>
       <c r="M30" s="19">
         <f t="shared" si="6"/>
-        <v>8654.313843320002</v>
+        <v>7350.9733922399992</v>
       </c>
       <c r="N30" s="22" t="e">
         <f t="shared" si="4"/>
@@ -2466,11 +2461,11 @@
       <c r="K31" s="19"/>
       <c r="L31" s="19">
         <f t="shared" si="7"/>
-        <v>8654.313843320002</v>
+        <v>7350.9733922399992</v>
       </c>
       <c r="M31" s="19">
         <f t="shared" si="6"/>
-        <v>8654.313843320002</v>
+        <v>7350.9733922399992</v>
       </c>
       <c r="N31" s="22" t="e">
         <f t="shared" si="4"/>
@@ -2496,7 +2491,7 @@
         <v>58</v>
       </c>
       <c r="D32" s="36" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E32" s="36">
         <v>1.18</v>
@@ -2521,11 +2516,11 @@
       <c r="K32" s="37"/>
       <c r="L32" s="37">
         <f t="shared" si="7"/>
-        <v>8654.313843320002</v>
+        <v>7350.9733922399992</v>
       </c>
       <c r="M32" s="37">
         <f t="shared" si="6"/>
-        <v>8654.313843320002</v>
+        <v>7350.9733922399992</v>
       </c>
       <c r="N32" s="22" t="e">
         <f t="shared" si="4"/>
@@ -2544,43 +2539,43 @@
       <c r="A33" s="36">
         <v>24</v>
       </c>
-      <c r="B33" s="52">
+      <c r="B33" s="39">
         <v>24</v>
       </c>
-      <c r="C33" s="52" t="s">
+      <c r="C33" s="39" t="s">
         <v>60</v>
       </c>
-      <c r="D33" s="65" t="s">
+      <c r="D33" s="66" t="s">
         <v>64</v>
       </c>
-      <c r="E33" s="52">
+      <c r="E33" s="39">
         <v>1.18</v>
       </c>
-      <c r="F33" s="52">
-        <v>0</v>
-      </c>
-      <c r="G33" s="52">
-        <v>0</v>
-      </c>
-      <c r="H33" s="53">
-        <v>0</v>
-      </c>
-      <c r="I33" s="54">
+      <c r="F33" s="39">
+        <v>0</v>
+      </c>
+      <c r="G33" s="39">
+        <v>0</v>
+      </c>
+      <c r="H33" s="40">
+        <v>0</v>
+      </c>
+      <c r="I33" s="41">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J33" s="54">
+      <c r="J33" s="41">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="K33" s="53"/>
-      <c r="L33" s="53">
+      <c r="K33" s="40"/>
+      <c r="L33" s="40">
         <f t="shared" si="7"/>
-        <v>8654.313843320002</v>
-      </c>
-      <c r="M33" s="53">
+        <v>7350.9733922399992</v>
+      </c>
+      <c r="M33" s="40">
         <f t="shared" si="6"/>
-        <v>8654.313843320002</v>
+        <v>7350.9733922399992</v>
       </c>
       <c r="N33" s="22" t="e">
         <f t="shared" si="4"/>
@@ -2612,19 +2607,19 @@
       </c>
       <c r="J34" s="30">
         <f>SUM(J10:J33)</f>
-        <v>290030.59259999986</v>
+        <v>407374.69320000004</v>
       </c>
       <c r="K34" s="29">
         <f>SUM(K10:K33)</f>
-        <v>3092.6699999999992</v>
+        <v>4343.9400000000005</v>
       </c>
       <c r="L34" s="29">
         <f>SUM(L10:L33)</f>
-        <v>733343.08575726021</v>
+        <v>622901.55041531997</v>
       </c>
       <c r="M34" s="29">
         <f>SUM(M10:M33)</f>
-        <v>1023391.6783572601</v>
+        <v>1030294.24361532</v>
       </c>
       <c r="N34" s="5"/>
       <c r="O34" s="2" t="e">
@@ -2636,19 +2631,19 @@
       <c r="A35" s="31" t="s">
         <v>61</v>
       </c>
-      <c r="C35" s="61" t="s">
+      <c r="C35" s="62" t="s">
         <v>62</v>
       </c>
-      <c r="D35" s="59"/>
-      <c r="E35" s="59"/>
-      <c r="F35" s="59"/>
-      <c r="G35" s="59"/>
-      <c r="H35" s="59"/>
-      <c r="I35" s="59"/>
-      <c r="J35" s="59"/>
-      <c r="K35" s="59"/>
-      <c r="L35" s="59"/>
-      <c r="M35" s="62"/>
+      <c r="D35" s="60"/>
+      <c r="E35" s="60"/>
+      <c r="F35" s="60"/>
+      <c r="G35" s="60"/>
+      <c r="H35" s="60"/>
+      <c r="I35" s="60"/>
+      <c r="J35" s="60"/>
+      <c r="K35" s="60"/>
+      <c r="L35" s="60"/>
+      <c r="M35" s="63"/>
       <c r="N35" s="31"/>
       <c r="O35" s="2" t="e">
         <f t="shared" si="9"/>
@@ -2666,86 +2661,86 @@
       <c r="H37" s="5"/>
       <c r="K37" s="34">
         <f>J34+L34</f>
-        <v>1023373.6783572601</v>
+        <v>1030276.24361532</v>
       </c>
       <c r="L37" s="34"/>
       <c r="O37" s="2"/>
     </row>
     <row r="38" spans="1:16" ht="0.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B38" s="63" t="s">
+      <c r="B38" s="64" t="s">
         <v>65</v>
       </c>
-      <c r="C38" s="64"/>
-      <c r="D38" s="64"/>
-      <c r="E38" s="64"/>
-      <c r="F38" s="64"/>
-      <c r="G38" s="64"/>
-      <c r="H38" s="64"/>
-      <c r="I38" s="64"/>
-      <c r="J38" s="64"/>
-      <c r="K38" s="64"/>
-      <c r="L38" s="64"/>
-      <c r="M38" s="64"/>
+      <c r="C38" s="65"/>
+      <c r="D38" s="65"/>
+      <c r="E38" s="65"/>
+      <c r="F38" s="65"/>
+      <c r="G38" s="65"/>
+      <c r="H38" s="65"/>
+      <c r="I38" s="65"/>
+      <c r="J38" s="65"/>
+      <c r="K38" s="65"/>
+      <c r="L38" s="65"/>
+      <c r="M38" s="65"/>
       <c r="O38" s="2"/>
     </row>
     <row r="39" spans="1:16" ht="33.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B39" s="64"/>
-      <c r="C39" s="64"/>
-      <c r="D39" s="64"/>
-      <c r="E39" s="64"/>
-      <c r="F39" s="64"/>
-      <c r="G39" s="64"/>
-      <c r="H39" s="64"/>
-      <c r="I39" s="64"/>
-      <c r="J39" s="64"/>
-      <c r="K39" s="64"/>
-      <c r="L39" s="64"/>
-      <c r="M39" s="64"/>
+      <c r="B39" s="65"/>
+      <c r="C39" s="65"/>
+      <c r="D39" s="65"/>
+      <c r="E39" s="65"/>
+      <c r="F39" s="65"/>
+      <c r="G39" s="65"/>
+      <c r="H39" s="65"/>
+      <c r="I39" s="65"/>
+      <c r="J39" s="65"/>
+      <c r="K39" s="65"/>
+      <c r="L39" s="65"/>
+      <c r="M39" s="65"/>
       <c r="O39" s="2"/>
     </row>
     <row r="40" spans="1:16" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B40" s="64"/>
-      <c r="C40" s="64"/>
-      <c r="D40" s="64"/>
-      <c r="E40" s="64"/>
-      <c r="F40" s="64"/>
-      <c r="G40" s="64"/>
-      <c r="H40" s="64"/>
-      <c r="I40" s="64"/>
-      <c r="J40" s="64"/>
-      <c r="K40" s="64"/>
-      <c r="L40" s="64"/>
-      <c r="M40" s="64"/>
+      <c r="B40" s="65"/>
+      <c r="C40" s="65"/>
+      <c r="D40" s="65"/>
+      <c r="E40" s="65"/>
+      <c r="F40" s="65"/>
+      <c r="G40" s="65"/>
+      <c r="H40" s="65"/>
+      <c r="I40" s="65"/>
+      <c r="J40" s="65"/>
+      <c r="K40" s="65"/>
+      <c r="L40" s="65"/>
+      <c r="M40" s="65"/>
       <c r="O40" s="2"/>
     </row>
     <row r="41" spans="1:16" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B41" s="64"/>
-      <c r="C41" s="64"/>
-      <c r="D41" s="64"/>
-      <c r="E41" s="64"/>
-      <c r="F41" s="64"/>
-      <c r="G41" s="64"/>
-      <c r="H41" s="64"/>
-      <c r="I41" s="64"/>
-      <c r="J41" s="64"/>
-      <c r="K41" s="64"/>
-      <c r="L41" s="64"/>
-      <c r="M41" s="64"/>
+      <c r="B41" s="65"/>
+      <c r="C41" s="65"/>
+      <c r="D41" s="65"/>
+      <c r="E41" s="65"/>
+      <c r="F41" s="65"/>
+      <c r="G41" s="65"/>
+      <c r="H41" s="65"/>
+      <c r="I41" s="65"/>
+      <c r="J41" s="65"/>
+      <c r="K41" s="65"/>
+      <c r="L41" s="65"/>
+      <c r="M41" s="65"/>
       <c r="O41" s="2"/>
     </row>
     <row r="42" spans="1:16" ht="64.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B42" s="64"/>
-      <c r="C42" s="64"/>
-      <c r="D42" s="64"/>
-      <c r="E42" s="64"/>
-      <c r="F42" s="64"/>
-      <c r="G42" s="64"/>
-      <c r="H42" s="64"/>
-      <c r="I42" s="64"/>
-      <c r="J42" s="64"/>
-      <c r="K42" s="64"/>
-      <c r="L42" s="64"/>
-      <c r="M42" s="64"/>
+      <c r="B42" s="65"/>
+      <c r="C42" s="65"/>
+      <c r="D42" s="65"/>
+      <c r="E42" s="65"/>
+      <c r="F42" s="65"/>
+      <c r="G42" s="65"/>
+      <c r="H42" s="65"/>
+      <c r="I42" s="65"/>
+      <c r="J42" s="65"/>
+      <c r="K42" s="65"/>
+      <c r="L42" s="65"/>
+      <c r="M42" s="65"/>
       <c r="O42" s="2"/>
     </row>
     <row r="43" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -6617,21 +6612,21 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="58" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="59"/>
-      <c r="C1" s="59"/>
-      <c r="D1" s="59"/>
-      <c r="E1" s="59"/>
-      <c r="F1" s="59"/>
-      <c r="G1" s="59"/>
-      <c r="H1" s="59"/>
-      <c r="I1" s="59"/>
-      <c r="J1" s="59"/>
-      <c r="K1" s="59"/>
-      <c r="L1" s="59"/>
-      <c r="M1" s="60"/>
+      <c r="A1" s="59" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="60"/>
+      <c r="C1" s="60"/>
+      <c r="D1" s="60"/>
+      <c r="E1" s="60"/>
+      <c r="F1" s="60"/>
+      <c r="G1" s="60"/>
+      <c r="H1" s="60"/>
+      <c r="I1" s="60"/>
+      <c r="J1" s="60"/>
+      <c r="K1" s="60"/>
+      <c r="L1" s="60"/>
+      <c r="M1" s="61"/>
       <c r="N1" s="1"/>
       <c r="O1" s="2"/>
       <c r="P1" s="3"/>
@@ -8223,19 +8218,19 @@
       <c r="A35" s="31" t="s">
         <v>61</v>
       </c>
-      <c r="C35" s="61" t="s">
+      <c r="C35" s="62" t="s">
         <v>62</v>
       </c>
-      <c r="D35" s="59"/>
-      <c r="E35" s="59"/>
-      <c r="F35" s="59"/>
-      <c r="G35" s="59"/>
-      <c r="H35" s="59"/>
-      <c r="I35" s="59"/>
-      <c r="J35" s="59"/>
-      <c r="K35" s="59"/>
-      <c r="L35" s="59"/>
-      <c r="M35" s="62"/>
+      <c r="D35" s="60"/>
+      <c r="E35" s="60"/>
+      <c r="F35" s="60"/>
+      <c r="G35" s="60"/>
+      <c r="H35" s="60"/>
+      <c r="I35" s="60"/>
+      <c r="J35" s="60"/>
+      <c r="K35" s="60"/>
+      <c r="L35" s="60"/>
+      <c r="M35" s="63"/>
       <c r="N35" s="31"/>
       <c r="O35" s="2" t="e">
         <f t="shared" si="8"/>
